--- a/output/MVA_Implementation_Plan.xlsx
+++ b/output/MVA_Implementation_Plan.xlsx
@@ -509,7 +509,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>删除 (Disabled/Removed)</t>
+          <t>Disabled/Removed</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -531,7 +531,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>调整 (Adjusted)</t>
+          <t>Adjusted</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>转为参考图 (Reference Charts)</t>
+          <t>Reference Charts</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>加账户占比 (Account Proportion)</t>
+          <t>Account Proportion</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -597,7 +597,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>新增图表 (New Charts)</t>
+          <t>New Charts</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>新增图表函数 (Chart Functions)</t>
+          <t>Chart Functions</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>模型改动 (Model Change)</t>
+          <t>Model Change</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
